--- a/docs/extraction_DB/gwayeon_tips_guideline_2026_r2/Review.xlsx
+++ b/docs/extraction_DB/gwayeon_tips_guideline_2026_r2/Review.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>붙임1.+2026년+팁스TIPS+총괄+운영지침+2차+개정안+본문.hwp (규정 본문 — 11. 연구개발비 산정기준, 16. 관리 및 사용, 부칙) / 붙임2.+2026년+팁스TIPS+총괄+운영지침+2차+개정안+별지서식.hwp (별지 제1-③호 부록2 연구개발비 비목별 총괄표 — 편성 양식의 비목 구조와 재원 구성 조건)</t>
+          <t>붙임1.+2026년+팁스TIPS+총괄+운영지침+2차+개정안+본문.hwp (규정 본문 — 11. 연구개발비 산정기준, 16. 관리 및 사용, 부칙) / 붙임2.+2026년+팁스TIPS+총괄+운영지침+2차+개정안+별지서식.hwp (별지 제1-③호 부록2 연구개발비 비목별 총괄표 — 편성 양식의 비목 구조와 재원 구성 조건) / 공고문.pdf (2026년 팁스 창업기업 지원계획 수정 공고 — 트랙별 지원 한도·재원 비율·청년인력 의무채용)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>연구개발비 산정·사용 기준은 국가연구개발사업 연구개발비 사용 기준을 따르되(지침 11.가), 이 지침이 별도로 정한 사항을 우선 적용한다. 이 패키지는 지침이 별도로 정했거나 명시한 규칙만 추출했다. 인건비의 기존/신규(일반·청년의무)/외부 구분과 위탁 직접비·간접비 구분은 본문이 아니라 별지서식의 편성 양식에서 왔다.</t>
+          <t>연구개발비 산정·사용 기준은 국가연구개발사업 연구개발비 사용 기준을 따르되(지침 11.가), 이 지침이 별도로 정한 사항을 우선 적용한다. 이 패키지는 지침이 별도로 정했거나 명시한 규칙만 추출했다. 인건비의 기존/신규(일반·청년의무)/외부 구분과 위탁 직접비·간접비 구분은 본문이 아니라 별지서식의 편성 양식에서 왔다. 2026년 신규 모집은 일반·딥테크 두 트랙이며(글로벌트랙은 신규 과제 없이 타 사업과 통합), 지원 한도와 사업기간이 트랙마다 달라 팩을 나눴다.</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -3935,7 +3935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5522,6 +5522,138 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TIPS_GENERAL_GOV_FUND_800M</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>일반트랙 정부지원연구개발비 최대 8억원</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>FIXED_AMOUNT</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>FIXED_AMOUNT</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>800000000</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>정부지원연구개발비 총액</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>팁스 일반트랙의 정부지원연구개발비는 최대 8억원(사업기간 최대 2년)</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>NOT_ALLOWED</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>공고 1. 팁스(TIPS) 지원 개요·2026년 팁스 R&amp;D 일반트랙 창업기업 지원 내용</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>최대 8 억원 … 최대 2 년 … 총 연구개발비의 75% 이내</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>TIPS_DEEPTECH_GOV_FUND_1500M</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>딥테크트랙 정부지원연구개발비 최대 15억원</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>FIXED_AMOUNT</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>FIXED_AMOUNT</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>정부지원연구개발비 총액</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>팁스 딥테크트랙의 정부지원연구개발비는 최대 15억원(사업기간 최대 3년)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>NOT_ALLOWED</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>공고 3. 팁스 R&amp;D 딥테크트랙·2026년 팁스 R&amp;D 딥테크트랙 창업기업 지원 내용</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>최대 15 억원 … 최대 3 년 … 총 연구개발비의 75% 이내</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5533,7 +5665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6920,22 +7052,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TIPS-LAB-001</t>
+          <t>TIPS_GENERAL_GOV_FUND_800M</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>영리기관 연구실 소모성 비용 계상 불가</t>
+          <t>일반트랙 정부지원연구개발비 최대 8억원</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>ACTIVITY_LAB_OPERATION</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>DENY_WITH_EXCEPTIONS</t>
+          <t>상한</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -6945,22 +7077,22 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>NOT_ALLOWED</t>
+          <t>BLOCKING</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>영리기관은 연구실 운영에 필요한 소모성 비용을 계상할 수 없습니다. 사무용 기기·소프트웨어와 냉난방·환경유지비는 활용·관리 계획을 인정·승인받은 경우에만 계상할 수 있습니다.</t>
+          <t>팁스 일반트랙의 정부지원연구개발비는 최대 8억원(사업기간 최대 2년)</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>영리기관의 경우, 연구실운영비 중 연구실 운영에 필요한 소모성 비용은 계상할 수 없다.</t>
+          <t>최대 8 억원 … 최대 2 년 … 총 연구개발비의 75% 이내</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 연구활동비 라)</t>
+          <t>공고 1. 팁스(TIPS) 지원 개요·2026년 팁스 R&amp;D 일반트랙 창업기업 지원 내용</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -6977,22 +7109,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>TIPS-MTG-001</t>
+          <t>TIPS_DEEPTECH_GOV_FUND_1500M</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>내부직원 간 회의 식비 계상 불가</t>
+          <t>딥테크트랙 정부지원연구개발비 최대 15억원</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>ACTIVITY_MEETING</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>DENY</t>
+          <t>상한</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -7002,22 +7134,22 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>NOT_ALLOWED</t>
+          <t>BLOCKING</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>외부기관 참석 없이 단일 수행기관 내부직원 간에만 진행한 회의의 식비(다과 등)는 계상할 수 없습니다.</t>
+          <t>팁스 딥테크트랙의 정부지원연구개발비는 최대 15억원(사업기간 최대 3년)</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>다만, 상기 ②에도 불구하고 외부기관 참석 없이 단일 수행기관 내부직원 간의 회의비 중, 식비(다과 등)로 사용하는 경우 계상할 수 없다.</t>
+          <t>최대 15 억원 … 최대 3 년 … 총 연구개발비의 75% 이내</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 연구활동비 마)③</t>
+          <t>공고 3. 팁스 R&amp;D 딥테크트랙·2026년 팁스 R&amp;D 딥테크트랙 창업기업 지원 내용</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -7034,22 +7166,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TIPS-MTG-002</t>
+          <t>TIPS-LAB-001</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>회의비 증빙자료</t>
+          <t>영리기관 연구실 소모성 비용 계상 불가</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>ACTIVITY_MEETING</t>
+          <t>ACTIVITY_LAB_OPERATION</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>EVIDENCE</t>
+          <t>DENY_WITH_EXCEPTIONS</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -7059,22 +7191,22 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>EVIDENCE_REQUIRED</t>
+          <t>NOT_ALLOWED</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>회의비는 내부결재문서 또는 회의록과 결제 증빙을 갖춰야 합니다. 부가세 포함 10만원 이하 회의비는 회의 목적·일시·장소·내용·참석자 명단이 포함된 자료로 대신할 수 있습니다.</t>
+          <t>영리기관은 연구실 운영에 필요한 소모성 비용을 계상할 수 없습니다. 사무용 기기·소프트웨어와 냉난방·환경유지비는 활용·관리 계획을 인정·승인받은 경우에만 계상할 수 있습니다.</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>단, 10만원 이하(부가세 포함) 회의비는 내부결재문서 또는 회의록을 별도의 증명자료(회의의 목적, 일시, 장소, 내용, 참석자 명단이 포함된 자료)로 대신할 수 있음</t>
+          <t>영리기관의 경우, 연구실운영비 중 연구실 운영에 필요한 소모성 비용은 계상할 수 없다.</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>붙임 비목별 증빙자료 &lt;회의비&gt;</t>
+          <t>지침 11.다.1) 연구활동비 라)</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -7091,12 +7223,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>TIPS-MTG-003</t>
+          <t>TIPS-MTG-001</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>외부인 참석 회의만 식비 계상</t>
+          <t>내부직원 간 회의 식비 계상 불가</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -7106,7 +7238,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>ALLOW_WITH_EVIDENCE</t>
+          <t>DENY</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -7116,22 +7248,22 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>RECOGNITION_REQUIRED</t>
+          <t>NOT_ALLOWED</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>해당 연구개발기관에 소속되지 않은 자가 참여하고 사전에 내부결재가 완료된 회의만 식비를 계상할 수 있습니다.</t>
+          <t>외부기관 참석 없이 단일 수행기관 내부직원 간에만 진행한 회의의 식비(다과 등)는 계상할 수 없습니다.</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>해당 연구개발기관에 소속되지 않은 자가 참여하는 회의 중 사전에 내부결재가 완료된 회의에 대해서는 식비를 계상할 수 있다.</t>
+          <t>다만, 상기 ②에도 불구하고 외부기관 참석 없이 단일 수행기관 내부직원 간의 회의비 중, 식비(다과 등)로 사용하는 경우 계상할 수 없다.</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 연구활동비 마)②</t>
+          <t>지침 11.다.1) 연구활동비 마)③</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -7148,22 +7280,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TIPS-TECH-001</t>
+          <t>TIPS-MTG-002</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>소속 전문가 비용 계상 불가</t>
+          <t>회의비 증빙자료</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>ACTIVITY_EXTERNAL_TECH</t>
+          <t>ACTIVITY_MEETING</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>DENY</t>
+          <t>EVIDENCE</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -7173,22 +7305,22 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>NOT_ALLOWED</t>
+          <t>EVIDENCE_REQUIRED</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>해당기관 소속 전문가를 위한 비용은 외부 전문기술 활용비로 계상할 수 없습니다.</t>
+          <t>회의비는 내부결재문서 또는 회의록과 결제 증빙을 갖춰야 합니다. 부가세 포함 10만원 이하 회의비는 회의 목적·일시·장소·내용·참석자 명단이 포함된 자료로 대신할 수 있습니다.</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>단, 해당기관 소속 전문가를 위한 비용은 계상할 수 없다.</t>
+          <t>단, 10만원 이하(부가세 포함) 회의비는 내부결재문서 또는 회의록을 별도의 증명자료(회의의 목적, 일시, 장소, 내용, 참석자 명단이 포함된 자료)로 대신할 수 있음</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 연구활동비 나)①</t>
+          <t>붙임 비목별 증빙자료 &lt;회의비&gt;</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -7205,22 +7337,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>TIPS-EQP-001</t>
+          <t>TIPS-MTG-003</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>3천만원 이상 장비 구축·운영계획 사전승인</t>
+          <t>외부인 참석 회의만 식비 계상</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>DIRECT_EQUIPMENT</t>
+          <t>ACTIVITY_MEETING</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>APPROVAL_REQUIRED</t>
+          <t>ALLOW_WITH_EVIDENCE</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -7230,22 +7362,22 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>PRIOR_APPROVAL_REQUIRED</t>
+          <t>RECOGNITION_REQUIRED</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>부가세 포함 3천만원 이상 연구시설·장비를 구입하려면 연구개발계획서에 구축·운영계획을 작성해 승인받고, 협약 시 도입계획서를 제출해야 합니다.</t>
+          <t>해당 연구개발기관에 소속되지 않은 자가 참여하고 사전에 내부결재가 완료된 회의만 식비를 계상할 수 있습니다.</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>외부로부터의 임차 등이 불가능하여 부가세 포함 3천만원 이상의 연구시설·장비 등을 불가피하게 구입하여야 하는 경우에 연구개발계획서에 연구시설·장비 구축·운영계획을 작성·제출하여야 하고, 이를 승인 받은 경우 협약 시에 연구시설·장비 도입계획서를 작성하여 제출하여야 한다.</t>
+          <t>해당 연구개발기관에 소속되지 않은 자가 참여하는 회의 중 사전에 내부결재가 완료된 회의에 대해서는 식비를 계상할 수 있다.</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 연구시설·장비비 다)</t>
+          <t>지침 11.다.1) 연구활동비 마)②</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -7262,22 +7394,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TIPS-EQP-002</t>
+          <t>TIPS-TECH-001</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>1억원 이상 장비 도입 심의요청</t>
+          <t>소속 전문가 비용 계상 불가</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>DIRECT_EQUIPMENT</t>
+          <t>ACTIVITY_EXTERNAL_TECH</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>APPROVAL_REQUIRED</t>
+          <t>DENY</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -7287,22 +7419,22 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>PRIOR_APPROVAL_REQUIRED</t>
+          <t>NOT_ALLOWED</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>부가세 포함 1억원 이상 연구시설·장비를 구입하려면 협약 시 연구장비도입 심의요청서를 제출해야 합니다.</t>
+          <t>해당기관 소속 전문가를 위한 비용은 외부 전문기술 활용비로 계상할 수 없습니다.</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>부가세 포함 1억원 이상의 연구시설·장비를 구입하여야 하는 경우에는 협약 시 연구장비도입 심의요청서를 작성하여 제출하여야 한다.</t>
+          <t>단, 해당기관 소속 전문가를 위한 비용은 계상할 수 없다.</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 연구시설·장비비 라)</t>
+          <t>지침 11.다.1) 연구활동비 나)①</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -7319,12 +7451,12 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>TIPS-EQP-003</t>
+          <t>TIPS-EQP-001</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>기 보유·외부 장비 우선 활용 원칙</t>
+          <t>3천만원 이상 장비 구축·운영계획 사전승인</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -7334,7 +7466,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>PROCEDURE</t>
+          <t>APPROVAL_REQUIRED</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -7344,22 +7476,22 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>INFORMATION_REQUIRED</t>
+          <t>PRIOR_APPROVAL_REQUIRED</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>연구시설·장비는 기 보유 장비와 대학·연구기관·지방중소벤처기업청 등의 장비를 우선 활용하는 것이 원칙입니다. 이때 발생하는 수수료 등 부대경비는 현금으로 계상할 수 있습니다.</t>
+          <t>부가세 포함 3천만원 이상 연구시설·장비를 구입하려면 연구개발계획서에 구축·운영계획을 작성해 승인받고, 협약 시 도입계획서를 제출해야 합니다.</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>연구개발과제 수행에 필요한 연구시설·장비는 연구개발기관의 기 보유 연구시설·장비 및 대학․연구기관 또는 지방중소벤처기업청 등의 연구시설·장비를 우선 활용하는 것을 원칙으로 한다.</t>
+          <t>외부로부터의 임차 등이 불가능하여 부가세 포함 3천만원 이상의 연구시설·장비 등을 불가피하게 구입하여야 하는 경우에 연구개발계획서에 연구시설·장비 구축·운영계획을 작성·제출하여야 하고, 이를 승인 받은 경우 협약 시에 연구시설·장비 도입계획서를 작성하여 제출하여야 한다.</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 연구시설·장비비 나)</t>
+          <t>지침 11.다.1) 연구시설·장비비 다)</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -7376,12 +7508,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TIPS-EQP-004</t>
+          <t>TIPS-EQP-002</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>연구 무관 개인용 컴퓨터 제외</t>
+          <t>1억원 이상 장비 도입 심의요청</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -7391,7 +7523,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>DENY</t>
+          <t>APPROVAL_REQUIRED</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -7401,22 +7533,22 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>NOT_ALLOWED</t>
+          <t>PRIOR_APPROVAL_REQUIRED</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>해당 연구수행과 관련 없는 개인용 컴퓨터는 연구시설·장비비로 계상할 수 없습니다.</t>
+          <t>부가세 포함 1억원 이상 연구시설·장비를 구입하려면 협약 시 연구장비도입 심의요청서를 제출해야 합니다.</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>해당 연구개발사업에 활용할 수 있는 연구시설·장비(해당 연구수행과 관련 없는 개인용 컴퓨터는 제외)</t>
+          <t>부가세 포함 1억원 이상의 연구시설·장비를 구입하여야 하는 경우에는 협약 시 연구장비도입 심의요청서를 작성하여 제출하여야 한다.</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 연구시설·장비비 가)</t>
+          <t>지침 11.다.1) 연구시설·장비비 라)</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -7433,22 +7565,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>TIPS-LBR-001</t>
+          <t>TIPS-EQP-003</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>대표자 배우자·직계존비속 참여 조건</t>
+          <t>기 보유·외부 장비 우선 활용 원칙</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>DIRECT_LABOR</t>
+          <t>DIRECT_EQUIPMENT</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>ELIGIBILITY</t>
+          <t>PROCEDURE</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -7458,22 +7590,22 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>RECOGNITION_REQUIRED</t>
+          <t>INFORMATION_REQUIRED</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>연구개발기관 대표자의 배우자 및 직계 존비속은 가업승계 등 불가피하게 과제에 참여하는 경우에만 참여연구자로 등록할 수 있습니다.</t>
+          <t>연구시설·장비는 기 보유 장비와 대학·연구기관·지방중소벤처기업청 등의 장비를 우선 활용하는 것이 원칙입니다. 이때 발생하는 수수료 등 부대경비는 현금으로 계상할 수 있습니다.</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>주관연구개발기관 등 연구개발기관 대표자의 배우자 및 직계 존비속은 가업승계 등 불가피하게 연구개발과제에 참여하는 경우 참여연구자로 등록할 수 있다.</t>
+          <t>연구개발과제 수행에 필요한 연구시설·장비는 연구개발기관의 기 보유 연구시설·장비 및 대학․연구기관 또는 지방중소벤처기업청 등의 연구시설·장비를 우선 활용하는 것을 원칙으로 한다.</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 인건비 나)</t>
+          <t>지침 11.다.1) 연구시설·장비비 나)</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -7490,22 +7622,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TIPS-LBR-006</t>
+          <t>TIPS-EQP-004</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>사업별 인건비 계상률 100% 초과 불가</t>
+          <t>연구 무관 개인용 컴퓨터 제외</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>DIRECT_LABOR</t>
+          <t>DIRECT_EQUIPMENT</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>LIMIT</t>
+          <t>DENY</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -7520,17 +7652,17 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>참여연구자는 각 사업별 인건비 계상률 100%를 초과할 수 없습니다. (참여율 기준이며 비목 편성 금액의 상한이 아닙니다)</t>
+          <t>해당 연구수행과 관련 없는 개인용 컴퓨터는 연구시설·장비비로 계상할 수 없습니다.</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>단, 참여연구자는 연구개발사업과 연계사업 모두 참여가 가능하나, 각 사업별 인건비 계상률 100%를 초과할 수 없다.</t>
+          <t>해당 연구개발사업에 활용할 수 있는 연구시설·장비(해당 연구수행과 관련 없는 개인용 컴퓨터는 제외)</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>지침 11.나.3)</t>
+          <t>지침 11.다.1) 연구시설·장비비 가)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -7547,12 +7679,12 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>TIPS-LBR-007</t>
+          <t>TIPS-LBR-001</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>신규 채용 인력 1인당 계상률 100%</t>
+          <t>대표자 배우자·직계존비속 참여 조건</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -7562,7 +7694,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>LIMIT</t>
+          <t>ELIGIBILITY</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -7572,22 +7704,22 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>NOT_ALLOWED</t>
+          <t>RECOGNITION_REQUIRED</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>신규 채용 인력은 1인당 인건비 계상률 100%까지 계상할 수 있습니다. (참여율 기준이며 비목 편성 금액의 상한이 아닙니다)</t>
+          <t>연구개발기관 대표자의 배우자 및 직계 존비속은 가업승계 등 불가피하게 과제에 참여하는 경우에만 참여연구자로 등록할 수 있습니다.</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>상기 라)에 따른 신규 채용 인력은 1인당 인건비 계상률 100%까지 계상할 수 있다.</t>
+          <t>주관연구개발기관 등 연구개발기관 대표자의 배우자 및 직계 존비속은 가업승계 등 불가피하게 연구개발과제에 참여하는 경우 참여연구자로 등록할 수 있다.</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 인건비 라)</t>
+          <t>지침 11.다.1) 인건비 나)</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -7604,12 +7736,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TIPS-LBR-002</t>
+          <t>TIPS-LBR-006</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>신규 채용 인력의 범위</t>
+          <t>사업별 인건비 계상률 100% 초과 불가</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -7619,7 +7751,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>CLASSIFICATION</t>
+          <t>LIMIT</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -7629,22 +7761,22 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>INFORMATION_REQUIRED</t>
+          <t>NOT_ALLOWED</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>신규 채용 인력은 채용일로부터 과제접수마감일까지의 기간이 6개월 이내인 연구자를 포함해 연구개발 종료일 이내에 채용된 연구자를 말합니다.</t>
+          <t>참여연구자는 각 사업별 인건비 계상률 100%를 초과할 수 없습니다. (참여율 기준이며 비목 편성 금액의 상한이 아닙니다)</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>신규 채용 인력은 채용일로부터 과제접수마감일까지의 기간이 6개월 이내인 연구자를 포함하여 연구개발 종료일 이내에 채용된 연구자를 말한다.</t>
+          <t>단, 참여연구자는 연구개발사업과 연계사업 모두 참여가 가능하나, 각 사업별 인건비 계상률 100%를 초과할 수 없다.</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 인건비 다)</t>
+          <t>지침 11.나.3)</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -7661,12 +7793,12 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>TIPS-LBR-003</t>
+          <t>TIPS-LBR-007</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>현금 인건비 계상 대상</t>
+          <t>신규 채용 인력 1인당 계상률 100%</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -7676,7 +7808,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>ALLOW_WITH_EVIDENCE</t>
+          <t>LIMIT</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -7686,22 +7818,22 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>RECOGNITION_REQUIRED</t>
+          <t>NOT_ALLOWED</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>인건비를 현금으로 계상하려면 인건비 비중이 높은 과제(산업기술표준분류상 지식서비스 분야 등), 중소·중견기업 신규채용 인력, 창업 7년(신산업 분야 10년) 이내 창업기업 소속 직원, 육아부담 시간선택제 여성연구원 중 하나에 해당해야 합니다.</t>
+          <t>신규 채용 인력은 1인당 인건비 계상률 100%까지 계상할 수 있습니다. (참여율 기준이며 비목 편성 금액의 상한이 아닙니다)</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>연구개발비 사용기준 제65조제4항제6호에 따른 연구개발과제 또는 참여연구자가 다음에 해당하는 경우에는 인건비를 현금으로 계상할 수 있다.</t>
+          <t>상기 라)에 따른 신규 채용 인력은 1인당 인건비 계상률 100%까지 계상할 수 있다.</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 인건비 마)</t>
+          <t>지침 11.다.1) 인건비 라)</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
@@ -7718,12 +7850,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TIPS-LBR-004</t>
+          <t>TIPS-LBR-002</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>인건비 3개월 주기 선집행</t>
+          <t>신규 채용 인력의 범위</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -7733,7 +7865,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>PROCEDURE</t>
+          <t>CLASSIFICATION</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -7743,22 +7875,22 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>RECOGNITION_REQUIRED</t>
+          <t>INFORMATION_REQUIRED</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>회계관리체계가 구비된 기관은 연구인력의 안정적 수급 필요성이 인정된 경우 협약 시작월부터 매 3개월 주기로 인건비를 미리 집행할 수 있습니다.</t>
+          <t>신규 채용 인력은 채용일로부터 과제접수마감일까지의 기간이 6개월 이내인 연구자를 포함해 연구개발 종료일 이내에 채용된 연구자를 말합니다.</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>인건비 등 회계관리체계가 구비된 주관연구개발기관, 위탁연구개발기관은 연구인력의 안정적인 수급 등의 필요성이 인정된 경우 협약 시작월을 시작으로 매 3개월 주기로 인건비를 미리 집행할 수 있다.</t>
+          <t>신규 채용 인력은 채용일로부터 과제접수마감일까지의 기간이 6개월 이내인 연구자를 포함하여 연구개발 종료일 이내에 채용된 연구자를 말한다.</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 인건비 사)</t>
+          <t>지침 11.다.1) 인건비 다)</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -7775,12 +7907,12 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>TIPS-LBR-005</t>
+          <t>TIPS-LBR-003</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>청년인력 초과채용 시 현금 대체</t>
+          <t>현금 인건비 계상 대상</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -7790,7 +7922,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>ALLOW</t>
+          <t>ALLOW_WITH_EVIDENCE</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -7805,17 +7937,17 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>의무채용 청년인력 외에 청년인력을 초과 채용한 과제는 기관부담 현금을 그 인건비만큼 현물로 대체할 수 있습니다. 협약 시 '신규인력 채용(예정) 확인서'를 제출해야 합니다.</t>
+          <t>인건비를 현금으로 계상하려면 인건비 비중이 높은 과제(산업기술표준분류상 지식서비스 분야 등), 중소·중견기업 신규채용 인력, 창업 7년(신산업 분야 10년) 이내 창업기업 소속 직원, 육아부담 시간선택제 여성연구원 중 하나에 해당해야 합니다.</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>단, 정부지원연구개발비에 비례하여 의무채용한 청년인력 외에 청년인력을 초과로 채용한 과제의 경우 현금 부담금을 해당 인건비만큼 현물로 대체할 수 있으며(영리기관에 지원되는 정부지원연구개발비 총액 기준 5억원 이상 과제의 청년인력 의무채용 1인의 인건비는 제외), 요령 제3조제1항에서 정한 중소기업기술개발사업 공고 시 관련 내용을 명시해야 한다.</t>
+          <t>연구개발비 사용기준 제65조제4항제6호에 따른 연구개발과제 또는 참여연구자가 다음에 해당하는 경우에는 인건비를 현금으로 계상할 수 있다.</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>지침 11.나.1) 다)</t>
+          <t>지침 11.다.1) 인건비 마)</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -7832,22 +7964,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TIPS-INC-001</t>
+          <t>TIPS-LBR-004</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>연구수당 최종평가 판정 조건</t>
+          <t>인건비 3개월 주기 선집행</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>DIRECT_INCENTIVE</t>
+          <t>DIRECT_LABOR</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>REQUIRE</t>
+          <t>PROCEDURE</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -7857,22 +7989,22 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>NOT_ALLOWED</t>
+          <t>RECOGNITION_REQUIRED</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>연구수당은 2차 최종평가를 거친 과제 중 우수·보통·미흡 판정을 받은 과제의 집행금액만 인정됩니다.</t>
+          <t>회계관리체계가 구비된 기관은 연구인력의 안정적 수급 필요성이 인정된 경우 협약 시작월부터 매 3개월 주기로 인건비를 미리 집행할 수 있습니다.</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>연구수당은 2차 최종평가를 거친 과제 중 “우수”, “보통”, “미흡” 판정을 받은 과제의 집행금액만 인정된다.</t>
+          <t>인건비 등 회계관리체계가 구비된 주관연구개발기관, 위탁연구개발기관은 연구인력의 안정적인 수급 등의 필요성이 인정된 경우 협약 시작월을 시작으로 매 3개월 주기로 인건비를 미리 집행할 수 있다.</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 연구수당 나)</t>
+          <t>지침 11.다.1) 인건비 사)</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -7889,22 +8021,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>TIPS-INC-002</t>
+          <t>TIPS-LBR-005</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>연구수당 관련 4대보험·퇴직금 인건비 계상 불가</t>
+          <t>청년인력 초과채용 시 현금 대체</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>DIRECT_INCENTIVE</t>
+          <t>DIRECT_LABOR</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>DENY</t>
+          <t>ALLOW</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -7914,22 +8046,22 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>NOT_ALLOWED</t>
+          <t>RECOGNITION_REQUIRED</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>연구수당 지급으로 발생하는 4대보험 기관부담금과 퇴직급여충당금은 인건비로 계상할 수 없습니다.</t>
+          <t>의무채용 청년인력 외에 청년인력을 초과 채용한 과제는 기관부담 현금을 그 인건비만큼 현물로 대체할 수 있습니다. 협약 시 '신규인력 채용(예정) 확인서'를 제출해야 합니다.</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>연구수당 지급으로 발생하는 4대보험 기관부담금과 퇴직급여충당금은 인건비로 계상할 수 없다.</t>
+          <t>단, 정부지원연구개발비에 비례하여 의무채용한 청년인력 외에 청년인력을 초과로 채용한 과제의 경우 현금 부담금을 해당 인건비만큼 현물로 대체할 수 있으며(영리기관에 지원되는 정부지원연구개발비 총액 기준 5억원 이상 과제의 청년인력 의무채용 1인의 인건비는 제외), 요령 제3조제1항에서 정한 중소기업기술개발사업 공고 시 관련 내용을 명시해야 한다.</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 연구수당 다)</t>
+          <t>지침 11.나.1) 다)</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -7946,17 +8078,17 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TIPS-SUB-001</t>
+          <t>TIPS-INC-001</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>위탁연구개발비도 동일 산정기준 적용</t>
+          <t>연구수당 최종평가 판정 조건</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>DIRECT_SUBCONTRACT</t>
+          <t>DIRECT_INCENTIVE</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -7971,22 +8103,22 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>INFORMATION_REQUIRED</t>
+          <t>NOT_ALLOWED</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>위탁연구개발비는 이 지침의 직접비·간접비 산정기준을 그대로 따라야 합니다.</t>
+          <t>연구수당은 2차 최종평가를 거친 과제 중 우수·보통·미흡 판정을 받은 과제의 집행금액만 인정됩니다.</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>위탁연구개발비는 이 지침 11. 다. 1) 직접비 및 2) 간접비의 기준에 따라야 한다.</t>
+          <t>연구수당은 2차 최종평가를 거친 과제 중 “우수”, “보통”, “미흡” 판정을 받은 과제의 집행금액만 인정된다.</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>지침 11.다.1) 위탁연구개발비 다)</t>
+          <t>지침 11.다.1) 연구수당 나)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -8003,22 +8135,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>TIPS-USE-001</t>
+          <t>TIPS-INC-002</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>10만원 이상 집행 시 전자세금계산서·카드영수증 원칙</t>
+          <t>연구수당 관련 4대보험·퇴직금 인건비 계상 불가</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>DIRECT_INCENTIVE</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>PAYMENT_METHOD</t>
+          <t>DENY</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -8028,22 +8160,22 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>EVIDENCE_REQUIRED</t>
+          <t>NOT_ALLOWED</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>10만원 이상 연구개발비를 집행할 때는 국세청 전자세금계산서(간이세금계산서 불인정) 또는 신용카드영수증 사용이 원칙입니다. 직전연도 매출액 3억원 미만 개인사업자와 거래할 때는 휴폐업 여부를 사전 확인하고 일반세금계산서를 사용할 수 있습니다.</t>
+          <t>연구수당 지급으로 발생하는 4대보험 기관부담금과 퇴직급여충당금은 인건비로 계상할 수 없습니다.</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>10만원 이상의 연구개발비를 집행할 때에는 국세청에서 발행하는 전자세금계산서(간이세금계산서는 불인정) 또는 신용카드영수증의 사용을 원칙으로 한다.</t>
+          <t>연구수당 지급으로 발생하는 4대보험 기관부담금과 퇴직급여충당금은 인건비로 계상할 수 없다.</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>지침 16.나.1) ④</t>
+          <t>지침 11.다.1) 연구수당 다)</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -8060,22 +8192,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TIPS-USE-002</t>
+          <t>TIPS-SUB-001</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>연구개발비관리시스템 증빙 등록 의무</t>
+          <t>위탁연구개발비도 동일 산정기준 적용</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>DIRECT_SUBCONTRACT</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>EVIDENCE</t>
+          <t>REQUIRE</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -8085,22 +8217,22 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>EVIDENCE_REQUIRED</t>
+          <t>INFORMATION_REQUIRED</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>연구개발비 지급 거래 건은 전자세금계산서·지출결의서·연구장비 실물 사진 등 증빙자료를 연구개발비관리시스템에 의무적으로 등록해야 합니다.</t>
+          <t>위탁연구개발비는 이 지침의 직접비·간접비 산정기준을 그대로 따라야 합니다.</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>연구개발비 지급 거래 건에 대해서는 전자세금계산서, 지출결의서, 연구장비 실물 사진 등의 관련 증빙자료를 의무적으로 연구개발비관리시스템에 등록하여야 한다.</t>
+          <t>위탁연구개발비는 이 지침 11. 다. 1) 직접비 및 2) 간접비의 기준에 따라야 한다.</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>지침 16.나.1) ⑤</t>
+          <t>지침 11.다.1) 위탁연구개발비 다)</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -8117,12 +8249,12 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>TIPS-USE-003</t>
+          <t>TIPS-USE-001</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>잔액 이월 시 연구수당·간접비 감액만 가능</t>
+          <t>10만원 이상 집행 시 전자세금계산서·카드영수증 원칙</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -8132,7 +8264,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>LIMIT</t>
+          <t>PAYMENT_METHOD</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -8142,22 +8274,22 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>NOT_ALLOWED</t>
+          <t>EVIDENCE_REQUIRED</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>연차별 사용 잔액은 차년도 동일 세부비목으로 이월하며, 필요 시 이월금 중 직접비(현물 제외)를 변경해 쓸 수 있습니다. 다만 연구수당과 간접비는 감액만 가능합니다.</t>
+          <t>10만원 이상 연구개발비를 집행할 때는 국세청 전자세금계산서(간이세금계산서 불인정) 또는 신용카드영수증 사용이 원칙입니다. 직전연도 매출액 3억원 미만 개인사업자와 거래할 때는 휴폐업 여부를 사전 확인하고 일반세금계산서를 사용할 수 있습니다.</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>연차별 연구개발비의 사용 잔액은 차년도 연구개발비의 동일 세부비목으로 이월하여 사용하되, 필요한 경우 이월금(계속비) 중 직접비(현물 제외)를 변경하여 사용할 수 있다. 단, 연구수당과 간접비는 감액만 가능하며, 이월금(계속비)은 차년도 연구개발비에 추가하여 사용한다.</t>
+          <t>10만원 이상의 연구개발비를 집행할 때에는 국세청에서 발행하는 전자세금계산서(간이세금계산서는 불인정) 또는 신용카드영수증의 사용을 원칙으로 한다.</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>지침 16.나.1) ⑩</t>
+          <t>지침 16.나.1) ④</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -8174,12 +8306,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TIPS-FND-001</t>
+          <t>TIPS-USE-002</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>연계사업과 중복 계상 금지</t>
+          <t>연구개발비관리시스템 증빙 등록 의무</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -8189,7 +8321,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>DENY</t>
+          <t>EVIDENCE</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -8199,22 +8331,22 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>NOT_ALLOWED</t>
+          <t>EVIDENCE_REQUIRED</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>동일한 물품 및 내역으로 연구개발사업의 연구개발비와 연계사업의 사업비를 중복 계상해 사용할 수 없습니다.</t>
+          <t>연구개발비 지급 거래 건은 전자세금계산서·지출결의서·연구장비 실물 사진 등 증빙자료를 연구개발비관리시스템에 의무적으로 등록해야 합니다.</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>주관연구개발기관은 동일한 물품 및 내역으로 연구개발사업의 연구개발비와 연계사업의 사업비를 중복계상하여 사용해서는 아니 된다.</t>
+          <t>연구개발비 지급 거래 건에 대해서는 전자세금계산서, 지출결의서, 연구장비 실물 사진 등의 관련 증빙자료를 의무적으로 연구개발비관리시스템에 등록하여야 한다.</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>지침 11.나.3)</t>
+          <t>지침 16.나.1) ⑤</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
@@ -8231,12 +8363,12 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>TIPS-FND-002</t>
+          <t>TIPS-USE-003</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>기관부담 현금 납부 기한</t>
+          <t>잔액 이월 시 연구수당·간접비 감액만 가능</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -8246,7 +8378,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>DEADLINE</t>
+          <t>LIMIT</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -8256,22 +8388,22 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>PROCEDURE_REQUIRED</t>
+          <t>NOT_ALLOWED</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>기관부담연구개발비 현금은 협약 체결 시 또는 연차보고서 '계속' 판정 시, 해당 연차 연구개발기간 종료 3개월 이내에 전문기관이 지정한 계좌에 입금해야 합니다.</t>
+          <t>연차별 사용 잔액은 차년도 동일 세부비목으로 이월하며, 필요 시 이월금 중 직접비(현물 제외)를 변경해 쓸 수 있습니다. 다만 연구수당과 간접비는 감액만 가능합니다.</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>기관부담연구개발비 현금은 협약 체결 시 또는 연차보고서 검토 결과 “계속” 판정 시 전문기관이 지정한 연구개발비 계좌에 해당 연차별 연구개발기간이 종료되기 3개월 이내에 입금하여야 한다.</t>
+          <t>연차별 연구개발비의 사용 잔액은 차년도 연구개발비의 동일 세부비목으로 이월하여 사용하되, 필요한 경우 이월금(계속비) 중 직접비(현물 제외)를 변경하여 사용할 수 있다. 단, 연구수당과 간접비는 감액만 가능하며, 이월금(계속비)은 차년도 연구개발비에 추가하여 사용한다.</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>지침 11.바.3)</t>
+          <t>지침 16.나.1) ⑩</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
@@ -8288,55 +8420,397 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
+          <t>TIPS-FND-001</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>연계사업과 중복 계상 금지</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>DENY</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>NOT_ALLOWED</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>동일한 물품 및 내역으로 연구개발사업의 연구개발비와 연계사업의 사업비를 중복 계상해 사용할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>주관연구개발기관은 동일한 물품 및 내역으로 연구개발사업의 연구개발비와 연계사업의 사업비를 중복계상하여 사용해서는 아니 된다.</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>지침 11.나.3)</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>SOURCE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>TIPS-FND-002</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>기관부담 현금 납부 기한</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>DEADLINE</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>PROCEDURE_REQUIRED</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>기관부담연구개발비 현금은 협약 체결 시 또는 연차보고서 '계속' 판정 시, 해당 연차 연구개발기간 종료 3개월 이내에 전문기관이 지정한 계좌에 입금해야 합니다.</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>기관부담연구개발비 현금은 협약 체결 시 또는 연차보고서 검토 결과 “계속” 판정 시 전문기관이 지정한 연구개발비 계좌에 해당 연차별 연구개발기간이 종료되기 3개월 이내에 입금하여야 한다.</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>지침 11.바.3)</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>SOURCE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
           <t>TIPS-FND-003</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>현물 미집행분 현금 반납</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>DEADLINE</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>MANUAL_REVIEW</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>PROCEDURE_REQUIRED</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>기관부담연구개발비 현물은 해당 연차 기간 내 RCMS 현물집행등록을 완료해야 하며, 미집행금액은 전액 현금으로 반납해야 합니다.</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>기관부담연구개발비-현물(D)는 해당 연차 기간 내 RCMS 현물집행등록을 완료해야 하며, 미집행금액은 전액 현금으로 반납</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>별지 제1-③호 부록2 연차별 연구개발비 총괄표</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>SOURCE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>TIPS_YOUTH_HIRING</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>정부지원연구개발비 5억원당 청년인력 1인 의무채용</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>DIRECT_LABOR</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>REQUIRE</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>INFORMATION_REQUIRED</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>정부지원연구개발비 5억원당 청년인력 1인을 신규 의무채용해야 하며, 협약서류에 채용계획을 포함해야 합니다. 1년 이상 고용을 유지해야 하고 중도 퇴사 시 2개월 이내 대체채용이 원칙입니다.</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>창업기업은 정부지원연구개발비 5 억원 당 청년인력 1 인을 신규로 의무로 채용해야 하며</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>공고 6. 유의사항·정부지원연구개발비 비례 청년인력 의무채용</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>SOURCE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TIPS_GENERAL_INVESTMENT</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>일반트랙 운영사 투자유치 요건</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>ELIGIBILITY</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>INFORMATION_REQUIRED</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>팁스 운영사로부터 2억원 이상 투자를 유치해야 합니다(본사가 비수도권이면 1억원 이상). 운영사 지분율은 30% 이하로 유지해야 합니다.</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>2 억원 이상 … 단 창업기업의 본사가 비수도권 ( 서울 경기 인천 제외 ) 에 소재할 경우, 1 억원 이상 투자 필요</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>공고 2. 팁스 R&amp;D 일반트랙·투자금 세부 요건</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>SOURCE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>TIPS_DEEPTECH_ELIGIBILITY</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>딥테크트랙 신청자격</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>ELIGIBILITY</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>INFORMATION_REQUIRED</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>팁스 일반트랙을 수행해 '완료' 판정을 받고 협약 이후 후속투자 5억원 이상을 유치한 기업이 대상입니다. 3억원 이상 투자한 팁스 운영사의 추천이 필요하고 퇴직연금제도 도입이 필수입니다.</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>팁스 일반트랙 를 수행하여 ’ 완료 ‘ 판정을 받은 기업 … 후속투자 5 억원 이상 투자유치 … 퇴직연금제도 도입 필수</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>공고 2. 주요 변경 사항·신청자격 R&amp;D(딥테크)</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>SOURCE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>TIPS_TECH_FEE</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>기술료 징수한도</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>LIMIT</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>MANUAL_REVIEW</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>INFORMATION_REQUIRED</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>기술료 징수한도는 실사용 정부출연금의 10% 이내입니다.</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>기술료 징수한도는 실사용 정부출연금의 10% 이내</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>공고 5. 기술료 징수</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>SOURCE_VERIFIED</t>
         </is>
